--- a/EddiewareOpeningRangeSetup/EddiewareOpeningRangeSetup/test_dates_SL_TP_Same_Bar_rev00.xlsx
+++ b/EddiewareOpeningRangeSetup/EddiewareOpeningRangeSetup/test_dates_SL_TP_Same_Bar_rev00.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k_99_\Desktop\codding\OpeningRangeSetup\EddiewareOpeningRangeSetup\EddiewareOpeningRangeSetup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C55E4D65-0242-4370-8708-2B678A7D2C67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{213EE412-CE47-4144-9276-0C0D1E707A91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
